--- a/RR_templates.xlsx
+++ b/RR_templates.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\RationalResources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GitHub\RationalResources\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="23250" yWindow="0" windowWidth="18375" windowHeight="8625" firstSheet="2" activeTab="2"/>
+    <workbookView xWindow="23250" yWindow="0" windowWidth="18375" windowHeight="8625"/>
   </bookViews>
   <sheets>
     <sheet name="Crust" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
     <author>Jadon Wade</author>
   </authors>
   <commentList>
-    <comment ref="K1" authorId="0" shapeId="0">
+    <comment ref="M1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -60,7 +60,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
+    <comment ref="N1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -84,7 +84,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
+    <comment ref="O1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -108,7 +108,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
+    <comment ref="P1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -253,7 +253,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="249">
   <si>
     <t>Zeonium</t>
   </si>
@@ -771,39 +771,9 @@
     <t>GeoCoolant</t>
   </si>
   <si>
-    <t>&lt; 5</t>
-  </si>
-  <si>
-    <t>Has lava seas</t>
-  </si>
-  <si>
-    <t>Has decent magnetosphere or tidal interaction</t>
-  </si>
-  <si>
     <t>Baseline</t>
   </si>
   <si>
-    <t>Is mostly lava ocean</t>
-  </si>
-  <si>
-    <t>5 ~ 15</t>
-  </si>
-  <si>
-    <t>15 ~ 35</t>
-  </si>
-  <si>
-    <t>35 ~ 55</t>
-  </si>
-  <si>
-    <t>55 ~ 75</t>
-  </si>
-  <si>
-    <t>&gt; 75</t>
-  </si>
-  <si>
-    <t>Is protoplanet</t>
-  </si>
-  <si>
     <t>70 ~ 80</t>
   </si>
   <si>
@@ -834,9 +804,6 @@
     <t>Ammonia ice world</t>
   </si>
   <si>
-    <t>Has lava lakes or is sunkissed</t>
-  </si>
-  <si>
     <t>Noble gas or Hydrogen ice world</t>
   </si>
   <si>
@@ -985,6 +952,54 @@
   </si>
   <si>
     <t>1B</t>
+  </si>
+  <si>
+    <t>Snowball</t>
+  </si>
+  <si>
+    <t>5 ~ 10</t>
+  </si>
+  <si>
+    <t>10 ~ 15</t>
+  </si>
+  <si>
+    <t>15 ~ 25</t>
+  </si>
+  <si>
+    <t>25 ~ 35</t>
+  </si>
+  <si>
+    <t>35 ~ 45</t>
+  </si>
+  <si>
+    <t>Modest magnetosphere or tidal interaction</t>
+  </si>
+  <si>
+    <t>Protoplanet</t>
+  </si>
+  <si>
+    <t>Mostly lava ocean</t>
+  </si>
+  <si>
+    <t>Lava seas</t>
+  </si>
+  <si>
+    <t>Lava lakes or angry volcanoes or sunkissed</t>
+  </si>
+  <si>
+    <t>Strong magnetosphere or tidal interaction</t>
+  </si>
+  <si>
+    <t>&lt;= 5</t>
+  </si>
+  <si>
+    <t>&gt;= 45</t>
+  </si>
+  <si>
+    <t>Ice-NitroCarbon</t>
+  </si>
+  <si>
+    <t>ExoIceC</t>
   </si>
 </sst>
 </file>
@@ -992,13 +1007,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="7">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="0.00_ ;[Red]\-0.00\ "/>
-    <numFmt numFmtId="170" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="0.00_ ;[Red]\-0.00\ "/>
+    <numFmt numFmtId="169" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="28" x14ac:knownFonts="1">
     <font>
@@ -1319,18 +1334,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1"/>
@@ -1368,13 +1383,13 @@
     <xf numFmtId="3" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="13" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="13" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1408,12 +1423,12 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1431,18 +1446,22 @@
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="5"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="7"/>
-    <xf numFmtId="168" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" xfId="2" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="7" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="168" fontId="4" fillId="3" borderId="1" xfId="2" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="7" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="4" fillId="3" borderId="1" xfId="2" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="26" fillId="3" borderId="4" xfId="6" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="26" fillId="3" borderId="4" xfId="6" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="2" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1453,9 +1472,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1745,21 +1761,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S44"/>
+  <dimension ref="A1:U44"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
     <col min="5" max="5" width="11.125" customWidth="1"/>
     <col min="6" max="6" width="10.125" customWidth="1"/>
     <col min="7" max="7" width="10.875" customWidth="1"/>
-    <col min="8" max="9" width="12.25" customWidth="1"/>
-    <col min="11" max="11" width="12.5" customWidth="1"/>
-    <col min="12" max="12" width="10.375" customWidth="1"/>
-    <col min="13" max="14" width="12.75" customWidth="1"/>
-    <col min="17" max="19" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="12.25" customWidth="1"/>
+    <col min="13" max="13" width="12.5" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="16" width="12.75" customWidth="1"/>
+    <col min="19" max="21" width="9.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>40</v>
       </c>
@@ -1787,35 +1803,44 @@
       <c r="I1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="J1" s="2"/>
+      <c r="J1" s="2" t="s">
+        <v>247</v>
+      </c>
       <c r="K1" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="P1" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>214</v>
-      </c>
       <c r="R1" s="2" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B2" s="1">
-        <f t="shared" ref="B2:I2" si="0">SUM(B4:B25)</f>
+        <f t="shared" ref="B2:J2" si="0">SUM(B4:B25)</f>
         <v>100</v>
       </c>
       <c r="C2" s="1">
@@ -1846,37 +1871,49 @@
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="J2" s="1"/>
+      <c r="J2" s="1">
+        <f t="shared" si="0"/>
+        <v>95</v>
+      </c>
       <c r="K2" s="1">
-        <f>SUM(K4:K25)</f>
-        <v>95</v>
-      </c>
-      <c r="L2" s="1">
-        <f>SUM(L4:L25)</f>
-        <v>96</v>
-      </c>
+        <f t="shared" ref="K2" si="1">SUM(K4:K25)</f>
+        <v>98</v>
+      </c>
+      <c r="L2" s="1"/>
       <c r="M2" s="1">
         <f>SUM(M4:M25)</f>
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N2" s="1">
         <f>SUM(N4:N25)</f>
-        <v>98</v>
+        <v>96</v>
+      </c>
+      <c r="O2" s="1">
+        <f>SUM(O4:O25)</f>
+        <v>96</v>
       </c>
       <c r="P2" s="1">
         <f>SUM(P4:P25)</f>
+        <v>98</v>
+      </c>
+      <c r="R2" s="1">
+        <f>SUM(R4:R25)</f>
         <v>65</v>
       </c>
-      <c r="Q2" s="1">
-        <f t="shared" ref="Q2:R2" si="1">SUM(Q4:Q25)</f>
+      <c r="S2" s="1">
+        <f t="shared" ref="S2:T2" si="2">SUM(S4:S25)</f>
         <v>26</v>
       </c>
-      <c r="R2" s="1">
-        <f t="shared" si="1"/>
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T2" s="1">
+        <f t="shared" si="2"/>
+        <v>38.5</v>
+      </c>
+      <c r="U2" s="1">
+        <f t="shared" ref="U2" si="3">SUM(U4:U25)</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>29</v>
       </c>
@@ -1904,23 +1941,23 @@
       <c r="I4">
         <v>2</v>
       </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="L4">
+      <c r="M4">
+        <v>2</v>
+      </c>
+      <c r="N4">
         <v>34</v>
       </c>
-      <c r="M4">
+      <c r="O4">
         <v>4</v>
       </c>
-      <c r="N4">
-        <v>3</v>
-      </c>
-      <c r="Q4" s="37"/>
-      <c r="R4" s="37"/>
+      <c r="P4">
+        <v>3</v>
+      </c>
       <c r="S4" s="37"/>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T4" s="37"/>
+      <c r="U4" s="37"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -1936,8 +1973,11 @@
       <c r="I5">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="J5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -1953,20 +1993,29 @@
       <c r="I6">
         <v>4</v>
       </c>
-      <c r="N6">
+      <c r="J6">
+        <v>12</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="P6">
         <v>15</v>
-      </c>
-      <c r="P6">
-        <v>22.5</v>
-      </c>
-      <c r="Q6">
-        <v>3</v>
       </c>
       <c r="R6">
         <v>22.5</v>
       </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S6">
+        <v>3</v>
+      </c>
+      <c r="T6">
+        <v>4</v>
+      </c>
+      <c r="U6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -1991,20 +2040,26 @@
       <c r="I7">
         <v>5</v>
       </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
       <c r="K7">
+        <v>2</v>
+      </c>
+      <c r="M7">
         <v>9</v>
       </c>
-      <c r="L7">
-        <v>3</v>
-      </c>
-      <c r="M7">
-        <v>3</v>
-      </c>
       <c r="N7">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="O7">
+        <v>3</v>
+      </c>
+      <c r="P7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -2020,20 +2075,20 @@
       <c r="E8">
         <v>5</v>
       </c>
-      <c r="K8">
-        <v>3</v>
-      </c>
-      <c r="L8">
-        <v>5</v>
-      </c>
       <c r="M8">
+        <v>3</v>
+      </c>
+      <c r="N8">
+        <v>5</v>
+      </c>
+      <c r="O8">
         <v>12</v>
       </c>
-      <c r="N8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -2061,20 +2116,26 @@
       <c r="I9">
         <v>5</v>
       </c>
+      <c r="J9">
+        <v>3</v>
+      </c>
       <c r="K9">
-        <v>5</v>
-      </c>
-      <c r="L9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M9">
+        <v>5</v>
+      </c>
+      <c r="N9">
+        <v>3</v>
+      </c>
+      <c r="O9">
         <v>15</v>
       </c>
-      <c r="N9">
+      <c r="P9">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -2096,20 +2157,20 @@
       <c r="G10">
         <v>2</v>
       </c>
-      <c r="K10">
-        <v>3</v>
-      </c>
-      <c r="L10">
+      <c r="M10">
+        <v>3</v>
+      </c>
+      <c r="N10">
         <v>6</v>
       </c>
-      <c r="M10">
+      <c r="O10">
         <v>10</v>
       </c>
-      <c r="N10">
+      <c r="P10">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -2122,11 +2183,17 @@
       <c r="I11">
         <v>5</v>
       </c>
-      <c r="P11">
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>4</v>
+      </c>
+      <c r="R11">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -2154,20 +2221,26 @@
       <c r="I12">
         <v>5</v>
       </c>
+      <c r="J12">
+        <v>2</v>
+      </c>
       <c r="K12">
-        <v>10</v>
-      </c>
-      <c r="L12">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M12">
         <v>10</v>
       </c>
       <c r="N12">
+        <v>7</v>
+      </c>
+      <c r="O12">
+        <v>10</v>
+      </c>
+      <c r="P12">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -2195,20 +2268,26 @@
       <c r="I13">
         <v>4</v>
       </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
       <c r="K13">
+        <v>2</v>
+      </c>
+      <c r="M13">
         <v>10</v>
-      </c>
-      <c r="L13">
-        <v>4</v>
-      </c>
-      <c r="M13">
-        <v>4</v>
       </c>
       <c r="N13">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="O13">
+        <v>4</v>
+      </c>
+      <c r="P13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -2218,11 +2297,15 @@
       <c r="I14" s="36">
         <v>29</v>
       </c>
-      <c r="R14">
+      <c r="J14" s="36">
+        <v>50</v>
+      </c>
+      <c r="K14" s="36"/>
+      <c r="T14">
         <v>22.5</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -2250,37 +2333,46 @@
       <c r="I15">
         <v>4</v>
       </c>
+      <c r="J15" s="36">
+        <v>1</v>
+      </c>
       <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="M15">
         <v>10</v>
       </c>
-      <c r="L15">
-        <v>3</v>
-      </c>
-      <c r="M15">
-        <v>5</v>
-      </c>
       <c r="N15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="O15">
+        <v>5</v>
+      </c>
+      <c r="P15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>19</v>
       </c>
       <c r="F16">
         <v>9</v>
       </c>
-      <c r="L16">
-        <v>5</v>
-      </c>
       <c r="N16">
+        <v>5</v>
+      </c>
+      <c r="P16">
         <v>4</v>
       </c>
-      <c r="Q16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S16">
+        <v>5</v>
+      </c>
+      <c r="U16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -2302,20 +2394,20 @@
       <c r="G17">
         <v>2</v>
       </c>
-      <c r="K17">
-        <v>3</v>
-      </c>
-      <c r="L17">
+      <c r="M17">
+        <v>3</v>
+      </c>
+      <c r="N17">
         <v>4</v>
       </c>
-      <c r="M17">
+      <c r="O17">
         <v>8</v>
       </c>
-      <c r="N17">
+      <c r="P17">
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>2</v>
       </c>
@@ -2343,29 +2435,35 @@
       <c r="I18">
         <v>4</v>
       </c>
+      <c r="J18">
+        <v>3</v>
+      </c>
       <c r="K18">
+        <v>7</v>
+      </c>
+      <c r="M18">
         <v>18</v>
       </c>
-      <c r="L18">
+      <c r="N18">
         <v>6</v>
       </c>
-      <c r="M18">
-        <v>5</v>
-      </c>
-      <c r="N18">
+      <c r="O18">
+        <v>5</v>
+      </c>
+      <c r="P18">
         <v>8</v>
       </c>
-      <c r="P18">
+      <c r="R18">
         <v>22.5</v>
       </c>
-      <c r="Q18">
+      <c r="S18">
         <v>12</v>
       </c>
-      <c r="R18">
+      <c r="T18">
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -2393,20 +2491,26 @@
       <c r="I19">
         <v>5</v>
       </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
       <c r="K19">
+        <v>4</v>
+      </c>
+      <c r="M19">
         <v>6</v>
       </c>
-      <c r="L19">
+      <c r="N19">
         <v>7</v>
       </c>
-      <c r="M19">
+      <c r="O19">
         <v>7</v>
       </c>
-      <c r="N19">
+      <c r="P19">
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>136</v>
       </c>
@@ -2431,20 +2535,26 @@
       <c r="H20">
         <v>1</v>
       </c>
+      <c r="J20">
+        <v>2</v>
+      </c>
       <c r="K20">
+        <v>3</v>
+      </c>
+      <c r="M20">
         <v>7</v>
       </c>
-      <c r="L20">
-        <v>3</v>
-      </c>
-      <c r="M20">
+      <c r="N20">
+        <v>3</v>
+      </c>
+      <c r="O20">
         <v>6</v>
       </c>
-      <c r="N20">
+      <c r="P20">
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -2472,20 +2582,26 @@
       <c r="I21">
         <v>5</v>
       </c>
+      <c r="J21">
+        <v>2</v>
+      </c>
       <c r="K21">
+        <v>2</v>
+      </c>
+      <c r="M21">
         <v>6</v>
       </c>
-      <c r="L21">
-        <v>3</v>
-      </c>
-      <c r="M21">
-        <v>5</v>
-      </c>
       <c r="N21">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O21">
+        <v>5</v>
+      </c>
+      <c r="P21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -2507,20 +2623,20 @@
       <c r="G22">
         <v>2</v>
       </c>
-      <c r="K22">
-        <v>3</v>
-      </c>
-      <c r="L22">
-        <v>3</v>
-      </c>
       <c r="M22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N22">
+        <v>3</v>
+      </c>
+      <c r="O22">
+        <v>2</v>
+      </c>
+      <c r="P22">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>1</v>
       </c>
@@ -2545,78 +2661,89 @@
       <c r="I23">
         <v>18</v>
       </c>
-      <c r="Q23">
+      <c r="J23">
+        <v>15</v>
+      </c>
+      <c r="K23">
+        <v>65</v>
+      </c>
+      <c r="S23">
         <v>6</v>
       </c>
-      <c r="R23">
+      <c r="T23">
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B29" s="1">
-        <f t="shared" ref="B29:I29" si="2">SUM(B31:B44)</f>
+        <f t="shared" ref="B29:H29" si="4">SUM(B31:B44)</f>
         <v>76</v>
       </c>
       <c r="C29" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>74</v>
       </c>
       <c r="D29" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>83</v>
       </c>
       <c r="E29" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>89</v>
       </c>
       <c r="F29" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>83</v>
       </c>
       <c r="G29" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>75</v>
       </c>
       <c r="H29" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>63</v>
       </c>
       <c r="I29" s="1">
-        <f t="shared" si="2"/>
+        <f>SUM(I31:I44)</f>
         <v>40</v>
       </c>
       <c r="J29" s="1"/>
       <c r="K29" s="1">
         <f>SUM(K31:K44)</f>
-        <v>82</v>
-      </c>
-      <c r="L29" s="1">
-        <f>SUM(L31:L44)</f>
-        <v>86</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="L29" s="1"/>
       <c r="M29" s="1">
         <f>SUM(M31:M44)</f>
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="N29" s="1">
         <f>SUM(N31:N44)</f>
+        <v>86</v>
+      </c>
+      <c r="O29" s="1">
+        <f>SUM(O31:O44)</f>
+        <v>93</v>
+      </c>
+      <c r="P29" s="1">
+        <f>SUM(P31:P44)</f>
         <v>72</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>13</v>
       </c>
@@ -2638,17 +2765,17 @@
       <c r="G31">
         <v>2</v>
       </c>
-      <c r="K31">
-        <v>3</v>
-      </c>
-      <c r="L31">
+      <c r="M31">
         <v>3</v>
       </c>
       <c r="N31">
+        <v>3</v>
+      </c>
+      <c r="P31">
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>12</v>
       </c>
@@ -2673,20 +2800,20 @@
       <c r="I32">
         <v>5</v>
       </c>
-      <c r="K32">
+      <c r="M32">
         <v>6</v>
       </c>
-      <c r="L32">
-        <v>3</v>
-      </c>
-      <c r="M32">
-        <v>3</v>
-      </c>
       <c r="N32">
+        <v>3</v>
+      </c>
+      <c r="O32">
+        <v>3</v>
+      </c>
+      <c r="P32">
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>11</v>
       </c>
@@ -2695,52 +2822,56 @@
         <v>12</v>
       </c>
       <c r="C33" s="36">
-        <f t="shared" ref="C33:N33" si="3">ROUNDUP(C9*1.6,0)</f>
+        <f t="shared" ref="C33:P33" si="5">ROUNDUP(C9*1.6,0)</f>
         <v>5</v>
       </c>
       <c r="D33" s="36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="E33" s="36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="F33" s="36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>26</v>
       </c>
       <c r="G33" s="36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>32</v>
       </c>
       <c r="H33" s="36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>29</v>
       </c>
       <c r="I33" s="36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="J33" s="36"/>
       <c r="K33" s="36">
-        <f t="shared" si="3"/>
+        <v>65</v>
+      </c>
+      <c r="L33" s="36"/>
+      <c r="M33" s="36">
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
-      <c r="L33" s="36">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="M33" s="36">
-        <f t="shared" si="3"/>
+      <c r="N33" s="36">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="O33" s="36">
+        <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="N33" s="36">
-        <f t="shared" si="3"/>
+      <c r="P33" s="36">
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>10</v>
       </c>
@@ -2762,17 +2893,17 @@
       <c r="G34">
         <v>2</v>
       </c>
-      <c r="K34">
+      <c r="M34">
         <v>6</v>
-      </c>
-      <c r="L34">
-        <v>4</v>
       </c>
       <c r="N34">
         <v>4</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="P34">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>9</v>
       </c>
@@ -2795,10 +2926,13 @@
         <v>5</v>
       </c>
       <c r="K35">
+        <v>4</v>
+      </c>
+      <c r="M35">
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>8</v>
       </c>
@@ -2823,20 +2957,22 @@
       <c r="H36" s="36"/>
       <c r="I36" s="36"/>
       <c r="J36" s="36"/>
-      <c r="K36" s="36">
+      <c r="K36" s="36"/>
+      <c r="L36" s="36"/>
+      <c r="M36" s="36">
         <v>6</v>
       </c>
-      <c r="L36" s="36">
+      <c r="N36" s="36">
         <v>15</v>
       </c>
-      <c r="M36" s="36">
+      <c r="O36" s="36">
         <v>15</v>
       </c>
-      <c r="N36" s="36">
+      <c r="P36" s="36">
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>7</v>
       </c>
@@ -2866,19 +3002,23 @@
       </c>
       <c r="J37" s="36"/>
       <c r="K37" s="36">
-        <v>10</v>
-      </c>
-      <c r="L37" s="36">
-        <v>7</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="L37" s="36"/>
       <c r="M37" s="36">
         <v>10</v>
       </c>
       <c r="N37" s="36">
+        <v>7</v>
+      </c>
+      <c r="O37" s="36">
         <v>10</v>
       </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="P37" s="36">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>6</v>
       </c>
@@ -2903,12 +3043,14 @@
       <c r="J38" s="36"/>
       <c r="K38" s="36"/>
       <c r="L38" s="36"/>
-      <c r="M38" s="36">
+      <c r="M38" s="36"/>
+      <c r="N38" s="36"/>
+      <c r="O38" s="36">
         <v>15</v>
       </c>
-      <c r="N38" s="36"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="P38" s="36"/>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>5</v>
       </c>
@@ -2938,19 +3080,23 @@
       </c>
       <c r="J39" s="36"/>
       <c r="K39" s="36">
+        <v>2</v>
+      </c>
+      <c r="L39" s="36"/>
+      <c r="M39" s="36">
         <v>10</v>
       </c>
-      <c r="L39" s="36">
-        <v>3</v>
-      </c>
-      <c r="M39" s="36">
-        <v>3</v>
-      </c>
       <c r="N39" s="36">
         <v>3</v>
       </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O39" s="36">
+        <v>3</v>
+      </c>
+      <c r="P39" s="36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>4</v>
       </c>
@@ -2966,15 +3112,17 @@
       <c r="I40" s="36"/>
       <c r="J40" s="36"/>
       <c r="K40" s="36"/>
-      <c r="L40" s="36">
+      <c r="L40" s="36"/>
+      <c r="M40" s="36"/>
+      <c r="N40" s="36">
         <v>30</v>
       </c>
-      <c r="M40" s="36">
+      <c r="O40" s="36">
         <v>9</v>
       </c>
-      <c r="N40" s="36"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="P40" s="36"/>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>3</v>
       </c>
@@ -2999,20 +3147,22 @@
       <c r="H41" s="36"/>
       <c r="I41" s="36"/>
       <c r="J41" s="36"/>
-      <c r="K41" s="36">
-        <v>3</v>
-      </c>
-      <c r="L41" s="36">
+      <c r="K41" s="36"/>
+      <c r="L41" s="36"/>
+      <c r="M41" s="36">
+        <v>3</v>
+      </c>
+      <c r="N41" s="36">
         <v>7</v>
       </c>
-      <c r="M41" s="36">
+      <c r="O41" s="36">
         <v>4</v>
       </c>
-      <c r="N41" s="36">
+      <c r="P41" s="36">
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>2</v>
       </c>
@@ -3021,52 +3171,56 @@
         <v>18</v>
       </c>
       <c r="C42" s="36">
-        <f t="shared" ref="C42:N42" si="4">C18</f>
+        <f t="shared" ref="C42:P42" si="6">C18</f>
         <v>18</v>
       </c>
       <c r="D42" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="E42" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>15</v>
       </c>
       <c r="F42" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="G42" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>9</v>
       </c>
       <c r="H42" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="I42" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="J42" s="36"/>
       <c r="K42" s="36">
-        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="L42" s="36"/>
+      <c r="M42" s="36">
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
-      <c r="L42" s="36">
-        <f t="shared" si="4"/>
+      <c r="N42" s="36">
+        <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="M42" s="36">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="N42" s="36">
-        <f t="shared" si="4"/>
+      <c r="O42" s="36">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="P42" s="36">
+        <f t="shared" si="6"/>
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>1</v>
       </c>
@@ -3083,8 +3237,10 @@
       <c r="L43" s="36"/>
       <c r="M43" s="36"/>
       <c r="N43" s="36"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O43" s="36"/>
+      <c r="P43" s="36"/>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>0</v>
       </c>
@@ -3093,48 +3249,50 @@
         <v>7</v>
       </c>
       <c r="C44" s="36">
-        <f t="shared" ref="C44:N44" si="5">C21</f>
+        <f t="shared" ref="C44:P44" si="7">C21</f>
         <v>6</v>
       </c>
       <c r="D44" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="E44" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="F44" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G44" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="H44" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="I44" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="J44" s="36"/>
-      <c r="K44" s="36">
-        <f t="shared" si="5"/>
+      <c r="K44" s="36"/>
+      <c r="L44" s="36"/>
+      <c r="M44" s="36">
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="L44" s="36">
-        <f t="shared" si="5"/>
-        <v>3</v>
-      </c>
-      <c r="M44" s="36">
-        <f t="shared" si="5"/>
-        <v>5</v>
-      </c>
       <c r="N44" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="O44" s="36">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="P44" s="36">
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
     </row>
@@ -3160,40 +3318,40 @@
         <v>40</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>211</v>
-      </c>
       <c r="F1" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>201</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>212</v>
       </c>
       <c r="N1" s="2"/>
     </row>
@@ -3256,37 +3414,37 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="33" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="B4" s="52"/>
       <c r="C4" s="52"/>
       <c r="D4" s="52"/>
       <c r="E4" s="52" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="F4" s="52" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="G4" s="52" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="H4" s="52" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="I4" s="52" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="J4" s="52" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="K4" s="52" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="L4" s="52" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="M4" s="52" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -3600,25 +3758,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="67" t="s">
         <v>162</v>
       </c>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="66" t="s">
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="68" t="s">
         <v>161</v>
       </c>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
     </row>
     <row r="2" spans="1:21" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="67"/>
+      <c r="A2" s="69"/>
       <c r="B2" s="44" t="s">
         <v>160</v>
       </c>
@@ -3719,22 +3877,22 @@
         <v>40</v>
       </c>
       <c r="L6" s="49" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="M6" s="41" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="N6" s="41" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="S6" s="49" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="T6" s="49" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="U6" s="49" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
@@ -3745,19 +3903,19 @@
         <v>8</v>
       </c>
       <c r="L7" s="50">
-        <v>5</v>
-      </c>
-      <c r="M7" s="48" t="s">
-        <v>181</v>
-      </c>
-      <c r="N7" s="48" t="s">
-        <v>182</v>
+        <v>6</v>
+      </c>
+      <c r="M7" s="66" t="s">
+        <v>246</v>
+      </c>
+      <c r="N7" s="66" t="s">
+        <v>240</v>
       </c>
       <c r="R7" s="64" t="s">
         <v>92</v>
       </c>
-      <c r="S7" s="69" t="s">
-        <v>238</v>
+      <c r="S7" s="65" t="s">
+        <v>227</v>
       </c>
       <c r="T7" s="47">
         <v>5</v>
@@ -3771,18 +3929,18 @@
         <v>163</v>
       </c>
       <c r="L8" s="50">
-        <v>4</v>
-      </c>
-      <c r="M8" s="48" t="s">
-        <v>180</v>
-      </c>
-      <c r="N8" s="48" t="s">
-        <v>176</v>
+        <v>5</v>
+      </c>
+      <c r="M8" s="66" t="s">
+        <v>238</v>
+      </c>
+      <c r="N8" s="66" t="s">
+        <v>241</v>
       </c>
       <c r="R8" s="64" t="s">
         <v>33</v>
       </c>
-      <c r="S8" s="69">
+      <c r="S8" s="65">
         <v>1</v>
       </c>
       <c r="T8" s="47">
@@ -3815,19 +3973,19 @@
         <v>3</v>
       </c>
       <c r="L9" s="50">
-        <v>3</v>
-      </c>
-      <c r="M9" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="N9" s="48" t="s">
-        <v>173</v>
+        <v>4</v>
+      </c>
+      <c r="M9" s="66" t="s">
+        <v>237</v>
+      </c>
+      <c r="N9" s="66" t="s">
+        <v>242</v>
       </c>
       <c r="R9" s="64" t="s">
         <v>90</v>
       </c>
-      <c r="S9" s="69" t="s">
-        <v>238</v>
+      <c r="S9" s="65" t="s">
+        <v>227</v>
       </c>
       <c r="T9" s="47">
         <v>5</v>
@@ -3844,19 +4002,19 @@
         <v>40</v>
       </c>
       <c r="L10" s="50">
-        <v>2</v>
-      </c>
-      <c r="M10" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="N10" s="48" t="s">
-        <v>193</v>
+        <v>3</v>
+      </c>
+      <c r="M10" s="66" t="s">
+        <v>236</v>
+      </c>
+      <c r="N10" s="66" t="s">
+        <v>243</v>
       </c>
       <c r="R10" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="S10" s="69" t="s">
-        <v>240</v>
+      <c r="S10" s="65" t="s">
+        <v>229</v>
       </c>
       <c r="T10" s="47">
         <v>1</v>
@@ -3888,19 +4046,19 @@
         <v>0.1</v>
       </c>
       <c r="L11" s="50">
-        <v>1</v>
-      </c>
-      <c r="M11" s="48" t="s">
-        <v>177</v>
-      </c>
-      <c r="N11" s="48" t="s">
-        <v>174</v>
+        <v>2</v>
+      </c>
+      <c r="M11" s="66" t="s">
+        <v>235</v>
+      </c>
+      <c r="N11" s="66" t="s">
+        <v>244</v>
       </c>
       <c r="R11" s="64" t="s">
         <v>30</v>
       </c>
-      <c r="S11" s="69" t="s">
-        <v>241</v>
+      <c r="S11" s="65" t="s">
+        <v>230</v>
       </c>
       <c r="T11" s="47">
         <v>3</v>
@@ -3917,19 +4075,19 @@
         <v>4</v>
       </c>
       <c r="L12" s="50">
-        <v>0</v>
-      </c>
-      <c r="M12" s="48" t="s">
-        <v>172</v>
-      </c>
-      <c r="N12" s="48" t="s">
-        <v>175</v>
+        <v>1</v>
+      </c>
+      <c r="M12" s="64" t="s">
+        <v>234</v>
+      </c>
+      <c r="N12" s="66" t="s">
+        <v>239</v>
       </c>
       <c r="R12" s="64" t="s">
         <v>89</v>
       </c>
-      <c r="S12" s="69" t="s">
-        <v>242</v>
+      <c r="S12" s="65" t="s">
+        <v>231</v>
       </c>
       <c r="T12" s="47">
         <v>1</v>
@@ -3960,13 +4118,20 @@
       <c r="G13" s="47">
         <v>3</v>
       </c>
-      <c r="M13" s="48"/>
-      <c r="N13" s="48"/>
+      <c r="L13" s="50">
+        <v>0</v>
+      </c>
+      <c r="M13" s="66" t="s">
+        <v>245</v>
+      </c>
+      <c r="N13" s="48" t="s">
+        <v>172</v>
+      </c>
       <c r="R13" s="64" t="s">
         <v>84</v>
       </c>
-      <c r="S13" s="69" t="s">
-        <v>239</v>
+      <c r="S13" s="65" t="s">
+        <v>228</v>
       </c>
       <c r="T13" s="47">
         <v>10</v>
@@ -4000,8 +4165,8 @@
       <c r="R14" s="64" t="s">
         <v>82</v>
       </c>
-      <c r="S14" s="69" t="s">
-        <v>243</v>
+      <c r="S14" s="65" t="s">
+        <v>232</v>
       </c>
       <c r="T14" s="47">
         <v>7</v>
@@ -4017,8 +4182,8 @@
       <c r="R15" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="S15" s="69" t="s">
-        <v>238</v>
+      <c r="S15" s="65" t="s">
+        <v>227</v>
       </c>
       <c r="T15" s="47">
         <v>5</v>
@@ -4165,7 +4330,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="47" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="B23" s="51">
         <f t="shared" ref="B23:J23" si="2">SUM(100-B3)</f>
@@ -4229,13 +4394,13 @@
       <c r="H25" s="48"/>
       <c r="I25" s="48"/>
       <c r="L25" s="49" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="M25" s="41" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="N25" s="41" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -4251,10 +4416,10 @@
         <v>5</v>
       </c>
       <c r="M26" s="48" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="N26" s="48" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
@@ -4270,10 +4435,10 @@
         <v>4</v>
       </c>
       <c r="M27" s="48" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="N27" s="48" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -4289,10 +4454,10 @@
         <v>3</v>
       </c>
       <c r="M28" s="48" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="N28" s="48" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="O28" s="50"/>
     </row>
@@ -4301,10 +4466,10 @@
         <v>2</v>
       </c>
       <c r="M29" s="48" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="N29" s="48" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="O29" s="50"/>
     </row>
@@ -4313,10 +4478,10 @@
         <v>1</v>
       </c>
       <c r="M30" s="48" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="N30" s="48" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
@@ -4324,10 +4489,10 @@
         <v>0</v>
       </c>
       <c r="M31" s="48" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="N31" s="48" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -4374,13 +4539,13 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="K1" s="2" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
       <c r="S1" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
@@ -4400,28 +4565,28 @@
         <v>100</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="I2" s="63" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="N2" s="63" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="V2">
         <v>7</v>
@@ -4460,7 +4625,7 @@
       <c r="R4" s="38"/>
       <c r="S4" s="38">
         <f t="shared" ref="S4:S23" ca="1" si="2">RANDBETWEEN(1,100)</f>
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="T4" s="38">
         <f t="shared" ref="T4:T23" ca="1" si="3">RANDBETWEEN(G4,H4)</f>
@@ -4468,7 +4633,7 @@
       </c>
       <c r="U4" s="38">
         <f t="shared" ref="U4:U23" ca="1" si="4">RANDBETWEEN(L4,M4)</f>
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
@@ -4484,9 +4649,9 @@
       <c r="H5">
         <v>90</v>
       </c>
-      <c r="I5" s="62">
+      <c r="I5" s="62" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>79</v>
+        <v>-</v>
       </c>
       <c r="N5" s="62" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -4495,11 +4660,11 @@
       <c r="R5" s="38"/>
       <c r="S5" s="38">
         <f t="shared" ca="1" si="2"/>
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="T5" s="38">
         <f t="shared" ca="1" si="3"/>
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="U5" s="38">
         <f t="shared" ca="1" si="4"/>
@@ -4524,7 +4689,7 @@
       </c>
       <c r="I6" s="62">
         <f t="shared" ca="1" si="0"/>
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="N6" s="62" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -4533,11 +4698,11 @@
       <c r="R6" s="38"/>
       <c r="S6" s="38">
         <f t="shared" ca="1" si="2"/>
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="T6" s="38">
         <f t="shared" ca="1" si="3"/>
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="U6" s="38">
         <f t="shared" ca="1" si="4"/>
@@ -4568,7 +4733,7 @@
       </c>
       <c r="I7" s="62">
         <f t="shared" ca="1" si="0"/>
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="K7">
         <v>40</v>
@@ -4581,19 +4746,19 @@
       </c>
       <c r="N7" s="62">
         <f t="shared" ca="1" si="1"/>
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="S7" s="38">
         <f t="shared" ca="1" si="2"/>
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="T7" s="38">
         <f t="shared" ca="1" si="3"/>
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="U7" s="38">
         <f t="shared" ca="1" si="4"/>
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
@@ -4622,13 +4787,13 @@
       <c r="M8">
         <v>10</v>
       </c>
-      <c r="N8" s="62">
+      <c r="N8" s="62" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>-</v>
       </c>
       <c r="S8" s="38">
         <f t="shared" ca="1" si="2"/>
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="T8" s="38">
         <f t="shared" ca="1" si="3"/>
@@ -4636,7 +4801,7 @@
       </c>
       <c r="U8" s="38">
         <f t="shared" ca="1" si="4"/>
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
@@ -4676,11 +4841,11 @@
       </c>
       <c r="N9" s="62">
         <f t="shared" ca="1" si="1"/>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S9" s="38">
         <f t="shared" ca="1" si="2"/>
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="T9" s="38">
         <f t="shared" ca="1" si="3"/>
@@ -4688,7 +4853,7 @@
       </c>
       <c r="U9" s="38">
         <f t="shared" ca="1" si="4"/>
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
@@ -4719,11 +4884,11 @@
       </c>
       <c r="N10" s="62">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="S10" s="38">
         <f t="shared" ca="1" si="2"/>
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="T10" s="38">
         <f t="shared" ca="1" si="3"/>
@@ -4731,7 +4896,7 @@
       </c>
       <c r="U10" s="38">
         <f t="shared" ca="1" si="4"/>
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
@@ -4750,9 +4915,9 @@
       <c r="H11">
         <v>90</v>
       </c>
-      <c r="I11" s="62" t="str">
+      <c r="I11" s="62">
         <f t="shared" ca="1" si="0"/>
-        <v>-</v>
+        <v>66</v>
       </c>
       <c r="N11" s="62" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -4760,11 +4925,11 @@
       </c>
       <c r="S11" s="38">
         <f t="shared" ca="1" si="2"/>
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="T11" s="38">
         <f t="shared" ca="1" si="3"/>
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="U11" s="38">
         <f t="shared" ca="1" si="4"/>
@@ -4795,7 +4960,7 @@
       </c>
       <c r="I12" s="62">
         <f t="shared" ca="1" si="0"/>
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="K12">
         <v>100</v>
@@ -4808,19 +4973,19 @@
       </c>
       <c r="N12" s="62">
         <f t="shared" ca="1" si="1"/>
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="S12" s="38">
         <f t="shared" ca="1" si="2"/>
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="T12" s="38">
         <f t="shared" ca="1" si="3"/>
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="U12" s="38">
         <f t="shared" ca="1" si="4"/>
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
@@ -4849,13 +5014,13 @@
       <c r="M13">
         <v>40</v>
       </c>
-      <c r="N13" s="62" t="str">
+      <c r="N13" s="62">
         <f t="shared" ca="1" si="1"/>
-        <v>-</v>
+        <v>35</v>
       </c>
       <c r="S13" s="38">
         <f t="shared" ca="1" si="2"/>
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="T13" s="38">
         <f t="shared" ca="1" si="3"/>
@@ -4863,7 +5028,7 @@
       </c>
       <c r="U13" s="38">
         <f t="shared" ca="1" si="4"/>
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
@@ -4881,7 +5046,7 @@
       </c>
       <c r="I14" s="62">
         <f t="shared" ca="1" si="0"/>
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="M14" s="36"/>
       <c r="N14" s="62" t="str">
@@ -4890,11 +5055,11 @@
       </c>
       <c r="S14" s="38">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="T14" s="38">
         <f t="shared" ca="1" si="3"/>
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="U14" s="38">
         <f t="shared" ca="1" si="4"/>
@@ -4925,7 +5090,7 @@
       </c>
       <c r="I15" s="62">
         <f t="shared" ca="1" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K15">
         <v>100</v>
@@ -4938,19 +5103,19 @@
       </c>
       <c r="N15" s="62">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S15" s="38">
         <f t="shared" ca="1" si="2"/>
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="T15" s="38">
         <f t="shared" ca="1" si="3"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U15" s="38">
         <f t="shared" ca="1" si="4"/>
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
@@ -4970,7 +5135,7 @@
       </c>
       <c r="S16" s="38">
         <f t="shared" ca="1" si="2"/>
-        <v>99</v>
+        <v>32</v>
       </c>
       <c r="T16" s="38">
         <f t="shared" ca="1" si="3"/>
@@ -5018,19 +5183,19 @@
       </c>
       <c r="N17" s="62">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="S17" s="38">
         <f t="shared" ca="1" si="2"/>
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="T17" s="38">
         <f t="shared" ca="1" si="3"/>
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="U17" s="38">
         <f t="shared" ca="1" si="4"/>
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
@@ -5057,7 +5222,7 @@
       </c>
       <c r="I18" s="62">
         <f t="shared" ca="1" si="0"/>
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="K18">
         <v>100</v>
@@ -5070,19 +5235,19 @@
       </c>
       <c r="N18" s="62">
         <f t="shared" ca="1" si="1"/>
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="S18" s="38">
         <f t="shared" ca="1" si="2"/>
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="T18" s="38">
         <f t="shared" ca="1" si="3"/>
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="U18" s="38">
         <f t="shared" ca="1" si="4"/>
-        <v>68</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
@@ -5109,7 +5274,7 @@
       </c>
       <c r="I19" s="62">
         <f t="shared" ca="1" si="0"/>
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="K19">
         <v>100</v>
@@ -5122,19 +5287,19 @@
       </c>
       <c r="N19" s="62">
         <f t="shared" ca="1" si="1"/>
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="S19" s="38">
         <f t="shared" ca="1" si="2"/>
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="T19" s="38">
         <f t="shared" ca="1" si="3"/>
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="U19" s="38">
         <f t="shared" ca="1" si="4"/>
-        <v>48</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
@@ -5161,7 +5326,7 @@
       </c>
       <c r="I20" s="62">
         <f t="shared" ca="1" si="0"/>
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K20">
         <v>80</v>
@@ -5174,19 +5339,19 @@
       </c>
       <c r="N20" s="62">
         <f t="shared" ca="1" si="1"/>
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="S20" s="38">
         <f t="shared" ca="1" si="2"/>
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="T20" s="38">
         <f t="shared" ca="1" si="3"/>
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="U20" s="38">
         <f t="shared" ca="1" si="4"/>
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
@@ -5215,13 +5380,13 @@
       <c r="M21">
         <v>10</v>
       </c>
-      <c r="N21" s="62">
+      <c r="N21" s="62" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>-</v>
       </c>
       <c r="S21" s="38">
         <f t="shared" ca="1" si="2"/>
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="T21" s="38">
         <f t="shared" ca="1" si="3"/>
@@ -5229,7 +5394,7 @@
       </c>
       <c r="U21" s="38">
         <f t="shared" ca="1" si="4"/>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
@@ -5265,7 +5430,7 @@
       </c>
       <c r="S22" s="38">
         <f t="shared" ca="1" si="2"/>
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="T22" s="38">
         <f t="shared" ca="1" si="3"/>
@@ -5273,7 +5438,7 @@
       </c>
       <c r="U22" s="38">
         <f t="shared" ca="1" si="4"/>
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
@@ -5294,7 +5459,7 @@
       </c>
       <c r="I23" s="62">
         <f t="shared" ca="1" si="0"/>
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="N23" s="62" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -5302,11 +5467,11 @@
       </c>
       <c r="S23" s="38">
         <f t="shared" ca="1" si="2"/>
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="T23" s="38">
         <f t="shared" ca="1" si="3"/>
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="U23" s="38">
         <f t="shared" ca="1" si="4"/>
@@ -5321,7 +5486,7 @@
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="K26" s="2" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
@@ -5344,28 +5509,28 @@
         <v>0</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="I27" s="63" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="N27" s="63" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -5385,13 +5550,13 @@
       <c r="M29">
         <v>50</v>
       </c>
-      <c r="N29" s="62">
+      <c r="N29" s="62" t="str">
         <f ca="1">IF(S29&gt;K29,"-",U29)</f>
-        <v>31</v>
+        <v>-</v>
       </c>
       <c r="S29" s="38">
         <f t="shared" ref="S29:S42" ca="1" si="6">RANDBETWEEN(1,100)</f>
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="T29" s="38">
         <f ca="1">RANDBETWEEN(G29,H29)</f>
@@ -5399,7 +5564,7 @@
       </c>
       <c r="U29" s="38">
         <f ca="1">RANDBETWEEN(L29,M29)</f>
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -5434,15 +5599,15 @@
       </c>
       <c r="S30" s="38">
         <f t="shared" ca="1" si="6"/>
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="T30" s="38">
         <f t="shared" ref="T30:T42" ca="1" si="9">RANDBETWEEN(G30,H30)</f>
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="U30" s="38">
         <f t="shared" ref="U30:U42" ca="1" si="10">RANDBETWEEN(L30,M30)</f>
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -5464,7 +5629,7 @@
       </c>
       <c r="I31" s="62">
         <f t="shared" ca="1" si="7"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K31">
         <v>100</v>
@@ -5477,19 +5642,19 @@
       </c>
       <c r="N31" s="62">
         <f t="shared" ca="1" si="8"/>
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="S31" s="38">
         <f t="shared" ca="1" si="6"/>
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="T31" s="38">
         <f t="shared" ca="1" si="9"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="U31" s="38">
         <f t="shared" ca="1" si="10"/>
-        <v>61</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
@@ -5506,7 +5671,7 @@
       </c>
       <c r="S32" s="38">
         <f t="shared" ca="1" si="6"/>
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="T32" s="38">
         <f t="shared" ca="1" si="9"/>
@@ -5530,9 +5695,9 @@
       <c r="H33">
         <v>90</v>
       </c>
-      <c r="I33" s="62" t="str">
+      <c r="I33" s="62">
         <f t="shared" ca="1" si="7"/>
-        <v>-</v>
+        <v>72</v>
       </c>
       <c r="N33" s="62" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -5540,11 +5705,11 @@
       </c>
       <c r="S33" s="38">
         <f t="shared" ca="1" si="6"/>
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="T33" s="38">
         <f t="shared" ca="1" si="9"/>
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="U33" s="38">
         <f t="shared" ca="1" si="10"/>
@@ -5584,19 +5749,19 @@
       </c>
       <c r="N34" s="62">
         <f t="shared" ca="1" si="8"/>
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="S34" s="38">
         <f t="shared" ca="1" si="6"/>
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="T34" s="38">
         <f t="shared" ca="1" si="9"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="U34" s="38">
         <f t="shared" ca="1" si="10"/>
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
@@ -5618,7 +5783,7 @@
       </c>
       <c r="I35" s="62">
         <f t="shared" ca="1" si="7"/>
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="J35" s="36"/>
       <c r="K35">
@@ -5632,19 +5797,19 @@
       </c>
       <c r="N35" s="62">
         <f t="shared" ca="1" si="8"/>
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="S35" s="38">
         <f t="shared" ca="1" si="6"/>
-        <v>81</v>
+        <v>16</v>
       </c>
       <c r="T35" s="38">
         <f t="shared" ca="1" si="9"/>
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="U35" s="38">
         <f t="shared" ca="1" si="10"/>
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
@@ -5684,15 +5849,15 @@
       </c>
       <c r="S36" s="38">
         <f t="shared" ca="1" si="6"/>
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="T36" s="38">
         <f t="shared" ca="1" si="9"/>
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="U36" s="38">
         <f t="shared" ca="1" si="10"/>
-        <v>86</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -5714,7 +5879,7 @@
       </c>
       <c r="I37" s="62">
         <f t="shared" ca="1" si="7"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J37" s="36"/>
       <c r="K37">
@@ -5728,19 +5893,19 @@
       </c>
       <c r="N37" s="62">
         <f t="shared" ca="1" si="8"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S37" s="38">
         <f t="shared" ca="1" si="6"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="T37" s="38">
         <f t="shared" ca="1" si="9"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U37" s="38">
         <f t="shared" ca="1" si="10"/>
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
@@ -5768,7 +5933,7 @@
       </c>
       <c r="S38" s="38">
         <f t="shared" ca="1" si="6"/>
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="T38" s="38">
         <f t="shared" ca="1" si="9"/>
@@ -5796,9 +5961,9 @@
       <c r="H39" s="36">
         <v>30</v>
       </c>
-      <c r="I39" s="62" t="str">
+      <c r="I39" s="62">
         <f t="shared" ca="1" si="7"/>
-        <v>-</v>
+        <v>22</v>
       </c>
       <c r="J39" s="36"/>
       <c r="K39">
@@ -5810,21 +5975,21 @@
       <c r="M39">
         <v>30</v>
       </c>
-      <c r="N39" s="62" t="str">
+      <c r="N39" s="62">
         <f t="shared" ca="1" si="8"/>
-        <v>-</v>
+        <v>21</v>
       </c>
       <c r="S39" s="38">
         <f t="shared" ca="1" si="6"/>
-        <v>97</v>
+        <v>15</v>
       </c>
       <c r="T39" s="38">
         <f t="shared" ca="1" si="9"/>
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="U39" s="38">
         <f t="shared" ca="1" si="10"/>
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -5846,7 +6011,7 @@
       </c>
       <c r="I40" s="62">
         <f t="shared" ca="1" si="7"/>
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="K40">
         <v>100</v>
@@ -5859,19 +6024,19 @@
       </c>
       <c r="N40" s="62">
         <f t="shared" ca="1" si="8"/>
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="S40" s="38">
         <f t="shared" ca="1" si="6"/>
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="T40" s="38">
         <f t="shared" ca="1" si="9"/>
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="U40" s="38">
         <f t="shared" ca="1" si="10"/>
-        <v>49</v>
+        <v>65</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
@@ -5893,7 +6058,7 @@
       </c>
       <c r="I41" s="62">
         <f t="shared" ca="1" si="7"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J41" s="36"/>
       <c r="K41" s="36"/>
@@ -5905,11 +6070,11 @@
       </c>
       <c r="S41" s="38">
         <f t="shared" ca="1" si="6"/>
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="T41" s="38">
         <f t="shared" ca="1" si="9"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="U41" s="38">
         <f t="shared" ca="1" si="10"/>
@@ -5935,7 +6100,7 @@
       </c>
       <c r="I42" s="62">
         <f t="shared" ca="1" si="7"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K42">
         <v>100</v>
@@ -5948,19 +6113,19 @@
       </c>
       <c r="N42" s="62">
         <f t="shared" ca="1" si="8"/>
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="S42" s="38">
         <f t="shared" ca="1" si="6"/>
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="T42" s="38">
         <f t="shared" ca="1" si="9"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="U42" s="38">
         <f t="shared" ca="1" si="10"/>
-        <v>46</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -6832,10 +6997,10 @@
       <c r="S1" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="T1" s="68" t="s">
+      <c r="T1" s="70" t="s">
         <v>115</v>
       </c>
-      <c r="U1" s="68"/>
+      <c r="U1" s="70"/>
       <c r="V1" s="2" t="s">
         <v>143</v>
       </c>
@@ -11204,30 +11369,30 @@
   <sheetData>
     <row r="2" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="53" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="C2" s="53" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="D2" s="53" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="E2" s="53" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="F2" s="53" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="G2" s="53" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="H2" s="53" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A3" s="54" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="B3" s="55">
         <v>962</v>
@@ -11255,7 +11420,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="54" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="B4" s="56">
         <f>B3/2</f>
@@ -11267,12 +11432,12 @@
         <v>1014</v>
       </c>
       <c r="L4" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="54" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="D5" s="61">
         <f>(D3/$B$4)</f>
@@ -11299,12 +11464,12 @@
         <v>812</v>
       </c>
       <c r="L5" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="57" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="D6" s="6" t="str">
         <f>IF(K5&lt;C3,"Yes","No")</f>
@@ -11316,7 +11481,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="57" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="G8" s="7">
         <v>1.6880999999999999</v>
@@ -11327,7 +11492,7 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="57" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="G9" s="56">
         <f>G8*$B$3</f>
@@ -11340,7 +11505,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="57" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="D10" s="56">
         <f>$B$3+D3</f>
@@ -11421,7 +11586,7 @@
     </row>
     <row r="20" spans="1:17" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A20" s="24" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="B20" s="23">
         <v>962</v>
